--- a/salidas/empresas/VRTX.xlsx
+++ b/salidas/empresas/VRTX.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EPS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="EPS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Info" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -435,54 +447,54 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>precio_ajustado</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>precio_cierre</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>volumen</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pe</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>acciones_circulacion</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>market_cap</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>rotacion</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>38748</v>
       </c>
       <c r="B2" t="n">
@@ -501,7 +513,7 @@
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>38776</v>
       </c>
       <c r="B3" t="n">
@@ -520,7 +532,7 @@
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>38807</v>
       </c>
       <c r="B4" t="n">
@@ -539,7 +551,7 @@
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>38837</v>
       </c>
       <c r="B5" t="n">
@@ -558,7 +570,7 @@
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>38868</v>
       </c>
       <c r="B6" t="n">
@@ -577,7 +589,7 @@
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>38898</v>
       </c>
       <c r="B7" t="n">
@@ -596,7 +608,7 @@
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>38929</v>
       </c>
       <c r="B8" t="n">
@@ -615,7 +627,7 @@
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>38960</v>
       </c>
       <c r="B9" t="n">
@@ -634,7 +646,7 @@
       <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>38990</v>
       </c>
       <c r="B10" t="n">
@@ -653,7 +665,7 @@
       <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>39021</v>
       </c>
       <c r="B11" t="n">
@@ -672,7 +684,7 @@
       <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>39051</v>
       </c>
       <c r="B12" t="n">
@@ -691,7 +703,7 @@
       <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>39082</v>
       </c>
       <c r="B13" t="n">
@@ -710,7 +722,7 @@
       <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>39113</v>
       </c>
       <c r="B14" t="n">
@@ -729,7 +741,7 @@
       <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>39141</v>
       </c>
       <c r="B15" t="n">
@@ -748,7 +760,7 @@
       <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>39172</v>
       </c>
       <c r="B16" t="n">
@@ -767,7 +779,7 @@
       <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>39202</v>
       </c>
       <c r="B17" t="n">
@@ -786,7 +798,7 @@
       <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>39233</v>
       </c>
       <c r="B18" t="n">
@@ -805,7 +817,7 @@
       <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>39263</v>
       </c>
       <c r="B19" t="n">
@@ -824,7 +836,7 @@
       <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>39294</v>
       </c>
       <c r="B20" t="n">
@@ -843,7 +855,7 @@
       <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>39325</v>
       </c>
       <c r="B21" t="n">
@@ -862,7 +874,7 @@
       <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>39355</v>
       </c>
       <c r="B22" t="n">
@@ -881,7 +893,7 @@
       <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>39386</v>
       </c>
       <c r="B23" t="n">
@@ -900,7 +912,7 @@
       <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>39416</v>
       </c>
       <c r="B24" t="n">
@@ -919,7 +931,7 @@
       <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>39447</v>
       </c>
       <c r="B25" t="n">
@@ -938,7 +950,7 @@
       <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>39478</v>
       </c>
       <c r="B26" t="n">
@@ -957,7 +969,7 @@
       <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>39507</v>
       </c>
       <c r="B27" t="n">
@@ -976,7 +988,7 @@
       <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>39538</v>
       </c>
       <c r="B28" t="n">
@@ -995,7 +1007,7 @@
       <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>39568</v>
       </c>
       <c r="B29" t="n">
@@ -1014,7 +1026,7 @@
       <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>39599</v>
       </c>
       <c r="B30" t="n">
@@ -1033,7 +1045,7 @@
       <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>39629</v>
       </c>
       <c r="B31" t="n">
@@ -1052,7 +1064,7 @@
       <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>39660</v>
       </c>
       <c r="B32" t="n">
@@ -1071,7 +1083,7 @@
       <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>39691</v>
       </c>
       <c r="B33" t="n">
@@ -1090,7 +1102,7 @@
       <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>39721</v>
       </c>
       <c r="B34" t="n">
@@ -1109,7 +1121,7 @@
       <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>39752</v>
       </c>
       <c r="B35" t="n">
@@ -1128,7 +1140,7 @@
       <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>39782</v>
       </c>
       <c r="B36" t="n">
@@ -1147,7 +1159,7 @@
       <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>39813</v>
       </c>
       <c r="B37" t="n">
@@ -1166,7 +1178,7 @@
       <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>39844</v>
       </c>
       <c r="B38" t="n">
@@ -1185,7 +1197,7 @@
       <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>39872</v>
       </c>
       <c r="B39" t="n">
@@ -1204,7 +1216,7 @@
       <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>39903</v>
       </c>
       <c r="B40" t="n">
@@ -1223,7 +1235,7 @@
       <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>39933</v>
       </c>
       <c r="B41" t="n">
@@ -1242,7 +1254,7 @@
       <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>39964</v>
       </c>
       <c r="B42" t="n">
@@ -1261,7 +1273,7 @@
       <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>39994</v>
       </c>
       <c r="B43" t="n">
@@ -1280,7 +1292,7 @@
       <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>40025</v>
       </c>
       <c r="B44" t="n">
@@ -1299,7 +1311,7 @@
       <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>40056</v>
       </c>
       <c r="B45" t="n">
@@ -1318,7 +1330,7 @@
       <c r="I45" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>40086</v>
       </c>
       <c r="B46" t="n">
@@ -1337,7 +1349,7 @@
       <c r="I46" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>40117</v>
       </c>
       <c r="B47" t="n">
@@ -1356,7 +1368,7 @@
       <c r="I47" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>40147</v>
       </c>
       <c r="B48" t="n">
@@ -1375,7 +1387,7 @@
       <c r="I48" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>40178</v>
       </c>
       <c r="B49" t="n">
@@ -1394,7 +1406,7 @@
       <c r="I49" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>40209</v>
       </c>
       <c r="B50" t="n">
@@ -1413,7 +1425,7 @@
       <c r="I50" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>40237</v>
       </c>
       <c r="B51" t="n">
@@ -1432,7 +1444,7 @@
       <c r="I51" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>40268</v>
       </c>
       <c r="B52" t="n">
@@ -1451,7 +1463,7 @@
       <c r="I52" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>40298</v>
       </c>
       <c r="B53" t="n">
@@ -1470,7 +1482,7 @@
       <c r="I53" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>40329</v>
       </c>
       <c r="B54" t="n">
@@ -1495,7 +1507,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>40359</v>
       </c>
       <c r="B55" t="n">
@@ -1520,7 +1532,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>40390</v>
       </c>
       <c r="B56" t="n">
@@ -1545,7 +1557,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>40421</v>
       </c>
       <c r="B57" t="n">
@@ -1570,7 +1582,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>40451</v>
       </c>
       <c r="B58" t="n">
@@ -1595,7 +1607,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>40482</v>
       </c>
       <c r="B59" t="n">
@@ -1620,7 +1632,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>40512</v>
       </c>
       <c r="B60" t="n">
@@ -1645,7 +1657,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>40543</v>
       </c>
       <c r="B61" t="n">
@@ -1670,7 +1682,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>40574</v>
       </c>
       <c r="B62" t="n">
@@ -1695,7 +1707,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="B63" t="n">
@@ -1722,7 +1734,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>40633</v>
       </c>
       <c r="B64" t="n">
@@ -1749,7 +1761,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>40663</v>
       </c>
       <c r="B65" t="n">
@@ -1776,7 +1788,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>40694</v>
       </c>
       <c r="B66" t="n">
@@ -1803,7 +1815,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>40724</v>
       </c>
       <c r="B67" t="n">
@@ -1830,7 +1842,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>40755</v>
       </c>
       <c r="B68" t="n">
@@ -1857,7 +1869,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>40786</v>
       </c>
       <c r="B69" t="n">
@@ -1884,7 +1896,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>40816</v>
       </c>
       <c r="B70" t="n">
@@ -1911,7 +1923,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>40847</v>
       </c>
       <c r="B71" t="n">
@@ -1938,7 +1950,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>40877</v>
       </c>
       <c r="B72" t="n">
@@ -1965,7 +1977,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>40908</v>
       </c>
       <c r="B73" t="n">
@@ -1992,7 +2004,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>40939</v>
       </c>
       <c r="B74" t="n">
@@ -2019,7 +2031,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="B75" t="n">
@@ -2048,7 +2060,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>40999</v>
       </c>
       <c r="B76" t="n">
@@ -2077,7 +2089,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>41029</v>
       </c>
       <c r="B77" t="n">
@@ -2106,7 +2118,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>41060</v>
       </c>
       <c r="B78" t="n">
@@ -2135,7 +2147,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>41090</v>
       </c>
       <c r="B79" t="n">
@@ -2164,7 +2176,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>41121</v>
       </c>
       <c r="B80" t="n">
@@ -2193,7 +2205,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>41152</v>
       </c>
       <c r="B81" t="n">
@@ -2222,7 +2234,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>41182</v>
       </c>
       <c r="B82" t="n">
@@ -2251,7 +2263,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="B83" t="n">
@@ -2280,7 +2292,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>41243</v>
       </c>
       <c r="B84" t="n">
@@ -2309,7 +2321,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>41274</v>
       </c>
       <c r="B85" t="n">
@@ -2338,7 +2350,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>41305</v>
       </c>
       <c r="B86" t="n">
@@ -2367,7 +2379,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="B87" t="n">
@@ -2396,7 +2408,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>41364</v>
       </c>
       <c r="B88" t="n">
@@ -2423,7 +2435,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="B89" t="n">
@@ -2450,7 +2462,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>41425</v>
       </c>
       <c r="B90" t="n">
@@ -2477,7 +2489,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>41455</v>
       </c>
       <c r="B91" t="n">
@@ -2504,7 +2516,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="B92" t="n">
@@ -2531,7 +2543,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>41517</v>
       </c>
       <c r="B93" t="n">
@@ -2558,7 +2570,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>41547</v>
       </c>
       <c r="B94" t="n">
@@ -2585,7 +2597,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="B95" t="n">
@@ -2612,7 +2624,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>41608</v>
       </c>
       <c r="B96" t="n">
@@ -2639,7 +2651,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>41639</v>
       </c>
       <c r="B97" t="n">
@@ -2666,7 +2678,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>41670</v>
       </c>
       <c r="B98" t="n">
@@ -2693,7 +2705,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="B99" t="n">
@@ -2720,7 +2732,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>41729</v>
       </c>
       <c r="B100" t="n">
@@ -2747,7 +2759,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="B101" t="n">
@@ -2774,7 +2786,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>41790</v>
       </c>
       <c r="B102" t="n">
@@ -2801,7 +2813,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>41820</v>
       </c>
       <c r="B103" t="n">
@@ -2828,7 +2840,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="B104" t="n">
@@ -2855,7 +2867,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>41882</v>
       </c>
       <c r="B105" t="n">
@@ -2882,7 +2894,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>41912</v>
       </c>
       <c r="B106" t="n">
@@ -2909,7 +2921,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="B107" t="n">
@@ -2936,7 +2948,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>41973</v>
       </c>
       <c r="B108" t="n">
@@ -2963,7 +2975,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>42004</v>
       </c>
       <c r="B109" t="n">
@@ -2990,7 +3002,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>42035</v>
       </c>
       <c r="B110" t="n">
@@ -3017,7 +3029,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>42063</v>
       </c>
       <c r="B111" t="n">
@@ -3044,7 +3056,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="B112" t="n">
@@ -3071,7 +3083,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="B113" t="n">
@@ -3098,7 +3110,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>42155</v>
       </c>
       <c r="B114" t="n">
@@ -3125,7 +3137,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>42185</v>
       </c>
       <c r="B115" t="n">
@@ -3152,7 +3164,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="B116" t="n">
@@ -3179,7 +3191,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>42247</v>
       </c>
       <c r="B117" t="n">
@@ -3206,7 +3218,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>42277</v>
       </c>
       <c r="B118" t="n">
@@ -3233,7 +3245,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>42308</v>
       </c>
       <c r="B119" t="n">
@@ -3260,7 +3272,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>42338</v>
       </c>
       <c r="B120" t="n">
@@ -3287,7 +3299,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>42369</v>
       </c>
       <c r="B121" t="n">
@@ -3314,7 +3326,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>42400</v>
       </c>
       <c r="B122" t="n">
@@ -3341,7 +3353,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="B123" t="n">
@@ -3368,7 +3380,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="B124" t="n">
@@ -3395,7 +3407,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>42490</v>
       </c>
       <c r="B125" t="n">
@@ -3422,7 +3434,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>42521</v>
       </c>
       <c r="B126" t="n">
@@ -3449,7 +3461,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="B127" t="n">
@@ -3476,7 +3488,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>42582</v>
       </c>
       <c r="B128" t="n">
@@ -3503,7 +3515,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>42613</v>
       </c>
       <c r="B129" t="n">
@@ -3530,7 +3542,7 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B130" t="n">
@@ -3557,7 +3569,7 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="B131" t="n">
@@ -3584,7 +3596,7 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>42704</v>
       </c>
       <c r="B132" t="n">
@@ -3611,7 +3623,7 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="B133" t="n">
@@ -3638,7 +3650,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>42766</v>
       </c>
       <c r="B134" t="n">
@@ -3665,7 +3677,7 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="B135" t="n">
@@ -3692,7 +3704,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B136" t="n">
@@ -3719,7 +3731,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>42855</v>
       </c>
       <c r="B137" t="n">
@@ -3748,7 +3760,7 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>42886</v>
       </c>
       <c r="B138" t="n">
@@ -3777,7 +3789,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B139" t="n">
@@ -3806,7 +3818,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>42947</v>
       </c>
       <c r="B140" t="n">
@@ -3835,7 +3847,7 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="B141" t="n">
@@ -3864,7 +3876,7 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="B142" t="n">
@@ -3893,7 +3905,7 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="B143" t="n">
@@ -3922,7 +3934,7 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>43069</v>
       </c>
       <c r="B144" t="n">
@@ -3951,7 +3963,7 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="B145" t="n">
@@ -3980,7 +3992,7 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="B146" t="n">
@@ -4009,7 +4021,7 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="B147" t="n">
@@ -4038,7 +4050,7 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="B148" t="n">
@@ -4067,7 +4079,7 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="B149" t="n">
@@ -4096,7 +4108,7 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="B150" t="n">
@@ -4125,7 +4137,7 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="B151" t="n">
@@ -4154,7 +4166,7 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="B152" t="n">
@@ -4183,7 +4195,7 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B153" t="n">
@@ -4212,7 +4224,7 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="B154" t="n">
@@ -4241,7 +4253,7 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="B155" t="n">
@@ -4270,7 +4282,7 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="B156" t="n">
@@ -4299,7 +4311,7 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="B157" t="n">
@@ -4328,7 +4340,7 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="B158" t="n">
@@ -4357,7 +4369,7 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="B159" t="n">
@@ -4386,7 +4398,7 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="B160" t="n">
@@ -4415,7 +4427,7 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="B161" t="n">
@@ -4444,7 +4456,7 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B162" t="n">
@@ -4473,7 +4485,7 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B163" t="n">
@@ -4502,7 +4514,7 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="B164" t="n">
@@ -4531,7 +4543,7 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B165" t="n">
@@ -4560,7 +4572,7 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B166" t="n">
@@ -4589,7 +4601,7 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B167" t="n">
@@ -4618,7 +4630,7 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B168" t="n">
@@ -4647,7 +4659,7 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B169" t="n">
@@ -4676,7 +4688,7 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B170" t="n">
@@ -4705,7 +4717,7 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B171" t="n">
@@ -4734,7 +4746,7 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B172" t="n">
@@ -4763,7 +4775,7 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B173" t="n">
@@ -4792,7 +4804,7 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B174" t="n">
@@ -4821,7 +4833,7 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B175" t="n">
@@ -4850,7 +4862,7 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B176" t="n">
@@ -4879,7 +4891,7 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B177" t="n">
@@ -4908,7 +4920,7 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B178" t="n">
@@ -4937,7 +4949,7 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B179" t="n">
@@ -4966,7 +4978,7 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B180" t="n">
@@ -4995,7 +5007,7 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B181" t="n">
@@ -5024,7 +5036,7 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B182" t="n">
@@ -5053,7 +5065,7 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B183" t="n">
@@ -5082,7 +5094,7 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B184" t="n">
@@ -5111,7 +5123,7 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B185" t="n">
@@ -5140,7 +5152,7 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B186" t="n">
@@ -5169,7 +5181,7 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B187" t="n">
@@ -5198,7 +5210,7 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B188" t="n">
@@ -5227,7 +5239,7 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B189" t="n">
@@ -5256,7 +5268,7 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B190" t="n">
@@ -5285,7 +5297,7 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B191" t="n">
@@ -5314,7 +5326,7 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B192" t="n">
@@ -5343,7 +5355,7 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B193" t="n">
@@ -5372,7 +5384,7 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B194" t="n">
@@ -5401,7 +5413,7 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B195" t="n">
@@ -5430,7 +5442,7 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B196" t="n">
@@ -5459,7 +5471,7 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B197" t="n">
@@ -5488,7 +5500,7 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B198" t="n">
@@ -5517,7 +5529,7 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B199" t="n">
@@ -5546,7 +5558,7 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B200" t="n">
@@ -5575,7 +5587,7 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B201" t="n">
@@ -5604,7 +5616,7 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B202" t="n">
@@ -5633,7 +5645,7 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B203" t="n">
@@ -5662,7 +5674,7 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B204" t="n">
@@ -5691,7 +5703,7 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B205" t="n">
@@ -5720,7 +5732,7 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B206" t="n">
@@ -5749,7 +5761,7 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B207" t="n">
@@ -5778,7 +5790,7 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B208" t="n">
@@ -5807,7 +5819,7 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B209" t="n">
@@ -5836,7 +5848,7 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B210" t="n">
@@ -5865,7 +5877,7 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B211" t="n">
@@ -5894,7 +5906,7 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B212" t="n">
@@ -5923,7 +5935,7 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B213" t="n">
@@ -5952,7 +5964,7 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B214" t="n">
@@ -5981,7 +5993,7 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B215" t="n">
@@ -6010,7 +6022,7 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B216" t="n">
@@ -6039,7 +6051,7 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B217" t="n">
@@ -6068,7 +6080,7 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B218" t="n">
@@ -6097,7 +6109,7 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B219" t="n">
@@ -6126,7 +6138,7 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B220" t="n">
@@ -6155,7 +6167,7 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B221" t="n">
@@ -6184,7 +6196,7 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B222" t="n">
@@ -6213,7 +6225,7 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B223" t="n">
@@ -6242,7 +6254,7 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B224" t="n">
@@ -6271,7 +6283,7 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B225" t="n">
@@ -6298,7 +6310,7 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B226" t="n">
@@ -6325,7 +6337,7 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B227" t="n">
@@ -6352,7 +6364,7 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B228" t="n">
@@ -6379,7 +6391,7 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B229" t="n">
@@ -6406,7 +6418,7 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B230" t="n">
@@ -6433,7 +6445,7 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B231" t="n">
@@ -6460,7 +6472,7 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B232" t="n">
@@ -6487,7 +6499,7 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B233" t="n">
@@ -6514,7 +6526,7 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B234" t="n">
@@ -6541,7 +6553,7 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B235" t="n">
@@ -6568,7 +6580,7 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B236" t="n">
@@ -6595,7 +6607,7 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B237" t="n">
@@ -6624,7 +6636,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B238" t="n">
@@ -6653,7 +6665,7 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B239" t="n">
@@ -6682,7 +6694,7 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B240" t="n">
@@ -6711,7 +6723,7 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B241" t="n">
@@ -6740,7 +6752,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B242" t="n">
@@ -6769,7 +6781,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B243" t="n">
@@ -6798,7 +6810,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B244" t="n">
@@ -6827,7 +6839,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B245" t="n">
@@ -6856,7 +6868,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B246" t="n">
@@ -6885,7 +6897,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B247" t="n">
@@ -6914,7 +6926,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B248" t="n">
@@ -6943,7 +6955,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B249" t="n">
@@ -6972,32 +6984,32 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B250" t="n">
-        <v>516.3400268554688</v>
+        <v>522.3800048828125</v>
       </c>
       <c r="C250" t="n">
-        <v>516.3400268554688</v>
+        <v>522.3800048828125</v>
       </c>
       <c r="D250" t="n">
-        <v>16982500</v>
+        <v>17923400</v>
       </c>
       <c r="E250" t="n">
         <v>17.17</v>
       </c>
       <c r="F250" t="n">
-        <v>30.07222055069707</v>
+        <v>30.423995625091</v>
       </c>
       <c r="G250" t="n">
         <v>253460924</v>
       </c>
       <c r="H250" t="n">
-        <v>130872020304.9719</v>
+        <v>132402918716.7222</v>
       </c>
       <c r="I250" t="n">
-        <v>0.06700243860864329</v>
+        <v>0.07071464791156526</v>
       </c>
     </row>
   </sheetData>
@@ -7029,75 +7041,75 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>eps_trimestral</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>filed_ttm</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39814</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>39903</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>40301</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -7133,13 +7145,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>39904</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>39994</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>40393</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -7175,13 +7187,13 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>39995</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>40086</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>40479</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -7217,13 +7229,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>40087</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40178</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>40591</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -7250,7 +7262,7 @@
       <c r="I5" t="n">
         <v>-3.73</v>
       </c>
-      <c r="J5" s="1" t="n">
+      <c r="J5" s="2" t="n">
         <v>40591</v>
       </c>
       <c r="K5" t="n">
@@ -7263,13 +7275,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40179</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40268</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>40301</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -7296,7 +7308,7 @@
       <c r="I6" t="n">
         <v>-3.52</v>
       </c>
-      <c r="J6" s="1" t="n">
+      <c r="J6" s="2" t="n">
         <v>40591</v>
       </c>
       <c r="K6" t="n">
@@ -7309,13 +7321,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40269</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40359</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
         <v>40393</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -7342,7 +7354,7 @@
       <c r="I7" t="n">
         <v>-3.53</v>
       </c>
-      <c r="J7" s="1" t="n">
+      <c r="J7" s="2" t="n">
         <v>40591</v>
       </c>
       <c r="K7" t="n">
@@ -7355,13 +7367,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40360</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40451</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>40479</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -7388,7 +7400,7 @@
       <c r="I8" t="n">
         <v>-3.73</v>
       </c>
-      <c r="J8" s="1" t="n">
+      <c r="J8" s="2" t="n">
         <v>40591</v>
       </c>
       <c r="K8" t="n">
@@ -7401,13 +7413,13 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40452</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40543</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="2" t="n">
         <v>40591</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -7434,7 +7446,7 @@
       <c r="I9" t="n">
         <v>-3.77</v>
       </c>
-      <c r="J9" s="1" t="n">
+      <c r="J9" s="2" t="n">
         <v>40591</v>
       </c>
       <c r="K9" t="n">
@@ -7447,13 +7459,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40544</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40633</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="2" t="n">
         <v>40669</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -7480,7 +7492,7 @@
       <c r="I10" t="n">
         <v>-3.81</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" s="2" t="n">
         <v>40669</v>
       </c>
       <c r="K10" t="n">
@@ -7493,13 +7505,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40634</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40724</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <v>40764</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -7526,7 +7538,7 @@
       <c r="I11" t="n">
         <v>-3.66</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11" s="2" t="n">
         <v>40764</v>
       </c>
       <c r="K11" t="n">
@@ -7539,13 +7551,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40725</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40816</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="2" t="n">
         <v>40850</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -7572,7 +7584,7 @@
       <c r="I12" t="n">
         <v>-1.6</v>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="J12" s="2" t="n">
         <v>40850</v>
       </c>
       <c r="K12" t="n">
@@ -7585,13 +7597,13 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>40817</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>40908</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="2" t="n">
         <v>40961</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -7618,7 +7630,7 @@
       <c r="I13" t="n">
         <v>0.03999999999999992</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="J13" s="2" t="n">
         <v>40961</v>
       </c>
       <c r="K13" t="n">
@@ -7631,13 +7643,13 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>40909</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>40999</v>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="2" t="n">
         <v>41039</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -7664,7 +7676,7 @@
       <c r="I14" t="n">
         <v>1.34</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="J14" s="2" t="n">
         <v>41039</v>
       </c>
       <c r="K14" t="n">
@@ -7677,13 +7689,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>41000</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>41090</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" s="2" t="n">
         <v>41129</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -7710,7 +7722,7 @@
       <c r="I15" t="n">
         <v>1.88</v>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="J15" s="2" t="n">
         <v>41129</v>
       </c>
       <c r="K15" t="n">
@@ -7723,13 +7735,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41091</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41182</v>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" s="2" t="n">
         <v>41219</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -7756,7 +7768,7 @@
       <c r="I16" t="n">
         <v>0.59</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="J16" s="2" t="n">
         <v>41219</v>
       </c>
       <c r="K16" t="n">
@@ -7769,13 +7781,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41183</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41274</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="2" t="n">
         <v>41334</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -7802,7 +7814,7 @@
       <c r="I17" t="n">
         <v>-0.5</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="J17" s="2" t="n">
         <v>41334</v>
       </c>
       <c r="K17" t="n">
@@ -7815,13 +7827,13 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41275</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41364</v>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" s="2" t="n">
         <v>41402</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -7848,7 +7860,7 @@
       <c r="I18" t="n">
         <v>-2.36</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="J18" s="2" t="n">
         <v>41402</v>
       </c>
       <c r="K18" t="n">
@@ -7861,13 +7873,13 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41365</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41455</v>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" s="2" t="n">
         <v>41488</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -7894,7 +7906,7 @@
       <c r="I19" t="n">
         <v>-2.31</v>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="J19" s="2" t="n">
         <v>41488</v>
       </c>
       <c r="K19" t="n">
@@ -7907,13 +7919,13 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41456</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41547</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="2" t="n">
         <v>41585</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -7940,7 +7952,7 @@
       <c r="I20" t="n">
         <v>-2.58</v>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="J20" s="2" t="n">
         <v>41585</v>
       </c>
       <c r="K20" t="n">
@@ -7953,13 +7965,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41548</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41639</v>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" s="2" t="n">
         <v>41681</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -7986,7 +7998,7 @@
       <c r="I21" t="n">
         <v>-2.04</v>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="J21" s="2" t="n">
         <v>41681</v>
       </c>
       <c r="K21" t="n">
@@ -7999,13 +8011,13 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41640</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41729</v>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" s="2" t="n">
         <v>41764</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -8032,7 +8044,7 @@
       <c r="I22" t="n">
         <v>-1.61</v>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="J22" s="2" t="n">
         <v>41764</v>
       </c>
       <c r="K22" t="n">
@@ -8045,13 +8057,13 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41730</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41820</v>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -8078,7 +8090,7 @@
       <c r="I23" t="n">
         <v>-2.03</v>
       </c>
-      <c r="J23" s="1" t="n">
+      <c r="J23" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="K23" t="n">
@@ -8091,13 +8103,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>41821</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>41912</v>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" s="2" t="n">
         <v>41949</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -8124,7 +8136,7 @@
       <c r="I24" t="n">
         <v>-2.21</v>
       </c>
-      <c r="J24" s="1" t="n">
+      <c r="J24" s="2" t="n">
         <v>41949</v>
       </c>
       <c r="K24" t="n">
@@ -8137,13 +8149,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>41913</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>42004</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C25" s="2" t="n">
         <v>42048</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -8170,7 +8182,7 @@
       <c r="I25" t="n">
         <v>-3.14</v>
       </c>
-      <c r="J25" s="1" t="n">
+      <c r="J25" s="2" t="n">
         <v>42048</v>
       </c>
       <c r="K25" t="n">
@@ -8183,13 +8195,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>42005</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42094</v>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C26" s="2" t="n">
         <v>42128</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -8216,7 +8228,7 @@
       <c r="I26" t="n">
         <v>-2.97</v>
       </c>
-      <c r="J26" s="1" t="n">
+      <c r="J26" s="2" t="n">
         <v>42128</v>
       </c>
       <c r="K26" t="n">
@@ -8229,13 +8241,13 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42095</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42185</v>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" s="2" t="n">
         <v>42220</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -8262,7 +8274,7 @@
       <c r="I27" t="n">
         <v>-3.069999999999999</v>
       </c>
-      <c r="J27" s="1" t="n">
+      <c r="J27" s="2" t="n">
         <v>42220</v>
       </c>
       <c r="K27" t="n">
@@ -8275,13 +8287,13 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42186</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42277</v>
       </c>
-      <c r="C28" s="1" t="n">
+      <c r="C28" s="2" t="n">
         <v>42307</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -8308,7 +8320,7 @@
       <c r="I28" t="n">
         <v>-2.74</v>
       </c>
-      <c r="J28" s="1" t="n">
+      <c r="J28" s="2" t="n">
         <v>42307</v>
       </c>
       <c r="K28" t="n">
@@ -8321,13 +8333,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42278</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42369</v>
       </c>
-      <c r="C29" s="1" t="n">
+      <c r="C29" s="2" t="n">
         <v>42416</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -8354,7 +8366,7 @@
       <c r="I29" t="n">
         <v>-2.31</v>
       </c>
-      <c r="J29" s="1" t="n">
+      <c r="J29" s="2" t="n">
         <v>42416</v>
       </c>
       <c r="K29" t="n">
@@ -8367,13 +8379,13 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42370</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42460</v>
       </c>
-      <c r="C30" s="1" t="n">
+      <c r="C30" s="2" t="n">
         <v>42493</v>
       </c>
       <c r="D30" t="inlineStr">
@@ -8400,7 +8412,7 @@
       <c r="I30" t="n">
         <v>-1.65</v>
       </c>
-      <c r="J30" s="1" t="n">
+      <c r="J30" s="2" t="n">
         <v>42493</v>
       </c>
       <c r="K30" t="n">
@@ -8413,13 +8425,13 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42461</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42551</v>
       </c>
-      <c r="C31" s="1" t="n">
+      <c r="C31" s="2" t="n">
         <v>42583</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -8446,7 +8458,7 @@
       <c r="I31" t="n">
         <v>-1.13</v>
       </c>
-      <c r="J31" s="1" t="n">
+      <c r="J31" s="2" t="n">
         <v>42583</v>
       </c>
       <c r="K31" t="n">
@@ -8459,13 +8471,13 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42552</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42643</v>
       </c>
-      <c r="C32" s="1" t="n">
+      <c r="C32" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="D32" t="inlineStr">
@@ -8492,7 +8504,7 @@
       <c r="I32" t="n">
         <v>-0.9000000000000001</v>
       </c>
-      <c r="J32" s="1" t="n">
+      <c r="J32" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="K32" t="n">
@@ -8505,13 +8517,13 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42644</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42735</v>
       </c>
-      <c r="C33" s="1" t="n">
+      <c r="C33" s="2" t="n">
         <v>42789</v>
       </c>
       <c r="D33" t="inlineStr">
@@ -8538,7 +8550,7 @@
       <c r="I33" t="n">
         <v>-0.4600000000000001</v>
       </c>
-      <c r="J33" s="1" t="n">
+      <c r="J33" s="2" t="n">
         <v>42789</v>
       </c>
       <c r="K33" t="n">
@@ -8551,13 +8563,13 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42736</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42825</v>
       </c>
-      <c r="C34" s="1" t="n">
+      <c r="C34" s="2" t="n">
         <v>42853</v>
       </c>
       <c r="D34" t="inlineStr">
@@ -8584,7 +8596,7 @@
       <c r="I34" t="n">
         <v>0.7</v>
       </c>
-      <c r="J34" s="1" t="n">
+      <c r="J34" s="2" t="n">
         <v>42853</v>
       </c>
       <c r="K34" t="n">
@@ -8597,13 +8609,13 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>42826</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>42916</v>
       </c>
-      <c r="C35" s="1" t="n">
+      <c r="C35" s="2" t="n">
         <v>42944</v>
       </c>
       <c r="D35" t="inlineStr">
@@ -8630,7 +8642,7 @@
       <c r="I35" t="n">
         <v>1.03</v>
       </c>
-      <c r="J35" s="1" t="n">
+      <c r="J35" s="2" t="n">
         <v>42944</v>
       </c>
       <c r="K35" t="n">
@@ -8643,13 +8655,13 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>42917</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>43008</v>
       </c>
-      <c r="C36" s="1" t="n">
+      <c r="C36" s="2" t="n">
         <v>43038</v>
       </c>
       <c r="D36" t="inlineStr">
@@ -8676,7 +8688,7 @@
       <c r="I36" t="n">
         <v>0.7799999999999999</v>
       </c>
-      <c r="J36" s="1" t="n">
+      <c r="J36" s="2" t="n">
         <v>43038</v>
       </c>
       <c r="K36" t="n">
@@ -8689,13 +8701,13 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>43009</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43100</v>
       </c>
-      <c r="C37" s="1" t="n">
+      <c r="C37" s="2" t="n">
         <v>43146</v>
       </c>
       <c r="D37" t="inlineStr">
@@ -8722,7 +8734,7 @@
       <c r="I37" t="n">
         <v>1.04</v>
       </c>
-      <c r="J37" s="1" t="n">
+      <c r="J37" s="2" t="n">
         <v>43146</v>
       </c>
       <c r="K37" t="n">
@@ -8735,13 +8747,13 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43101</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43190</v>
       </c>
-      <c r="C38" s="1" t="n">
+      <c r="C38" s="2" t="n">
         <v>43217</v>
       </c>
       <c r="D38" t="inlineStr">
@@ -8768,7 +8780,7 @@
       <c r="I38" t="n">
         <v>0.8600000000000001</v>
       </c>
-      <c r="J38" s="1" t="n">
+      <c r="J38" s="2" t="n">
         <v>43217</v>
       </c>
       <c r="K38" t="n">
@@ -8781,13 +8793,13 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43191</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43281</v>
       </c>
-      <c r="C39" s="1" t="n">
+      <c r="C39" s="2" t="n">
         <v>43307</v>
       </c>
       <c r="D39" t="inlineStr">
@@ -8814,7 +8826,7 @@
       <c r="I39" t="n">
         <v>1.59</v>
       </c>
-      <c r="J39" s="1" t="n">
+      <c r="J39" s="2" t="n">
         <v>43307</v>
       </c>
       <c r="K39" t="n">
@@ -8827,13 +8839,13 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43282</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43373</v>
       </c>
-      <c r="C40" s="1" t="n">
+      <c r="C40" s="2" t="n">
         <v>43398</v>
       </c>
       <c r="D40" t="inlineStr">
@@ -8860,7 +8872,7 @@
       <c r="I40" t="n">
         <v>2.5</v>
       </c>
-      <c r="J40" s="1" t="n">
+      <c r="J40" s="2" t="n">
         <v>43398</v>
       </c>
       <c r="K40" t="n">
@@ -8873,13 +8885,13 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43374</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43465</v>
       </c>
-      <c r="C41" s="1" t="n">
+      <c r="C41" s="2" t="n">
         <v>43509</v>
       </c>
       <c r="D41" t="inlineStr">
@@ -8906,7 +8918,7 @@
       <c r="I41" t="n">
         <v>8.08</v>
       </c>
-      <c r="J41" s="1" t="n">
+      <c r="J41" s="2" t="n">
         <v>43509</v>
       </c>
       <c r="K41" t="n">
@@ -8919,13 +8931,13 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43466</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43555</v>
       </c>
-      <c r="C42" s="1" t="n">
+      <c r="C42" s="2" t="n">
         <v>43586</v>
       </c>
       <c r="D42" t="inlineStr">
@@ -8952,7 +8964,7 @@
       <c r="I42" t="n">
         <v>8.299999999999999</v>
       </c>
-      <c r="J42" s="1" t="n">
+      <c r="J42" s="2" t="n">
         <v>43586</v>
       </c>
       <c r="K42" t="n">
@@ -8965,13 +8977,13 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43556</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43646</v>
       </c>
-      <c r="C43" s="1" t="n">
+      <c r="C43" s="2" t="n">
         <v>43678</v>
       </c>
       <c r="D43" t="inlineStr">
@@ -8998,7 +9010,7 @@
       <c r="I43" t="n">
         <v>8.529999999999999</v>
       </c>
-      <c r="J43" s="1" t="n">
+      <c r="J43" s="2" t="n">
         <v>43678</v>
       </c>
       <c r="K43" t="n">
@@ -9011,13 +9023,13 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43647</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43738</v>
       </c>
-      <c r="C44" s="1" t="n">
+      <c r="C44" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="D44" t="inlineStr">
@@ -9044,7 +9056,7 @@
       <c r="I44" t="n">
         <v>8.25</v>
       </c>
-      <c r="J44" s="1" t="n">
+      <c r="J44" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="K44" t="n">
@@ -9057,13 +9069,13 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43739</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43830</v>
       </c>
-      <c r="C45" s="1" t="n">
+      <c r="C45" s="2" t="n">
         <v>43874</v>
       </c>
       <c r="D45" t="inlineStr">
@@ -9090,7 +9102,7 @@
       <c r="I45" t="n">
         <v>4.51</v>
       </c>
-      <c r="J45" s="1" t="n">
+      <c r="J45" s="2" t="n">
         <v>43874</v>
       </c>
       <c r="K45" t="n">
@@ -9103,13 +9115,13 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>43831</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>43921</v>
       </c>
-      <c r="C46" s="1" t="n">
+      <c r="C46" s="2" t="n">
         <v>43952</v>
       </c>
       <c r="D46" t="inlineStr">
@@ -9136,7 +9148,7 @@
       <c r="I46" t="n">
         <v>5.77</v>
       </c>
-      <c r="J46" s="1" t="n">
+      <c r="J46" s="2" t="n">
         <v>43952</v>
       </c>
       <c r="K46" t="n">
@@ -9149,13 +9161,13 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>43922</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>44012</v>
       </c>
-      <c r="C47" s="1" t="n">
+      <c r="C47" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="D47" t="inlineStr">
@@ -9182,7 +9194,7 @@
       <c r="I47" t="n">
         <v>7.920000000000001</v>
       </c>
-      <c r="J47" s="1" t="n">
+      <c r="J47" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="K47" t="n">
@@ -9195,13 +9207,13 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44013</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44104</v>
       </c>
-      <c r="C48" s="1" t="n">
+      <c r="C48" s="2" t="n">
         <v>44134</v>
       </c>
       <c r="D48" t="inlineStr">
@@ -9228,7 +9240,7 @@
       <c r="I48" t="n">
         <v>10.23</v>
       </c>
-      <c r="J48" s="1" t="n">
+      <c r="J48" s="2" t="n">
         <v>44134</v>
       </c>
       <c r="K48" t="n">
@@ -9241,13 +9253,13 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44105</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44196</v>
       </c>
-      <c r="C49" s="1" t="n">
+      <c r="C49" s="2" t="n">
         <v>44238</v>
       </c>
       <c r="D49" t="inlineStr">
@@ -9274,7 +9286,7 @@
       <c r="I49" t="n">
         <v>10.3</v>
       </c>
-      <c r="J49" s="1" t="n">
+      <c r="J49" s="2" t="n">
         <v>44238</v>
       </c>
       <c r="K49" t="n">
@@ -9287,13 +9299,13 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44197</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="C50" s="1" t="n">
+      <c r="C50" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="D50" t="inlineStr">
@@ -9320,7 +9332,7 @@
       <c r="I50" t="n">
         <v>10.5</v>
       </c>
-      <c r="J50" s="1" t="n">
+      <c r="J50" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="K50" t="n">
@@ -9333,13 +9345,13 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44287</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44377</v>
       </c>
-      <c r="C51" s="1" t="n">
+      <c r="C51" s="2" t="n">
         <v>44407</v>
       </c>
       <c r="D51" t="inlineStr">
@@ -9366,7 +9378,7 @@
       <c r="I51" t="n">
         <v>7.58</v>
       </c>
-      <c r="J51" s="1" t="n">
+      <c r="J51" s="2" t="n">
         <v>44407</v>
       </c>
       <c r="K51" t="n">
@@ -9379,13 +9391,13 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44378</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44469</v>
       </c>
-      <c r="C52" s="1" t="n">
+      <c r="C52" s="2" t="n">
         <v>44503</v>
       </c>
       <c r="D52" t="inlineStr">
@@ -9412,7 +9424,7 @@
       <c r="I52" t="n">
         <v>8.33</v>
       </c>
-      <c r="J52" s="1" t="n">
+      <c r="J52" s="2" t="n">
         <v>44503</v>
       </c>
       <c r="K52" t="n">
@@ -9425,13 +9437,13 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44470</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44561</v>
       </c>
-      <c r="C53" s="1" t="n">
+      <c r="C53" s="2" t="n">
         <v>44601</v>
       </c>
       <c r="D53" t="inlineStr">
@@ -9458,7 +9470,7 @@
       <c r="I53" t="n">
         <v>9.01</v>
       </c>
-      <c r="J53" s="1" t="n">
+      <c r="J53" s="2" t="n">
         <v>44601</v>
       </c>
       <c r="K53" t="n">
@@ -9471,13 +9483,13 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44562</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44651</v>
       </c>
-      <c r="C54" s="1" t="n">
+      <c r="C54" s="2" t="n">
         <v>44687</v>
       </c>
       <c r="D54" t="inlineStr">
@@ -9504,7 +9516,7 @@
       <c r="I54" t="n">
         <v>9.48</v>
       </c>
-      <c r="J54" s="1" t="n">
+      <c r="J54" s="2" t="n">
         <v>44687</v>
       </c>
       <c r="K54" t="n">
@@ -9517,13 +9529,13 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44652</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44742</v>
       </c>
-      <c r="C55" s="1" t="n">
+      <c r="C55" s="2" t="n">
         <v>44778</v>
       </c>
       <c r="D55" t="inlineStr">
@@ -9550,7 +9562,7 @@
       <c r="I55" t="n">
         <v>12.35</v>
       </c>
-      <c r="J55" s="1" t="n">
+      <c r="J55" s="2" t="n">
         <v>44778</v>
       </c>
       <c r="K55" t="n">
@@ -9563,13 +9575,13 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44743</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44834</v>
       </c>
-      <c r="C56" s="1" t="n">
+      <c r="C56" s="2" t="n">
         <v>44862</v>
       </c>
       <c r="D56" t="inlineStr">
@@ -9596,7 +9608,7 @@
       <c r="I56" t="n">
         <v>12.66</v>
       </c>
-      <c r="J56" s="1" t="n">
+      <c r="J56" s="2" t="n">
         <v>44862</v>
       </c>
       <c r="K56" t="n">
@@ -9609,13 +9621,13 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>44835</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>44926</v>
       </c>
-      <c r="C57" s="1" t="n">
+      <c r="C57" s="2" t="n">
         <v>44967</v>
       </c>
       <c r="D57" t="inlineStr">
@@ -9642,7 +9654,7 @@
       <c r="I57" t="n">
         <v>12.82</v>
       </c>
-      <c r="J57" s="1" t="n">
+      <c r="J57" s="2" t="n">
         <v>44967</v>
       </c>
       <c r="K57" t="n">
@@ -9655,13 +9667,13 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>44927</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>45016</v>
       </c>
-      <c r="C58" s="1" t="n">
+      <c r="C58" s="2" t="n">
         <v>45048</v>
       </c>
       <c r="D58" t="inlineStr">
@@ -9688,7 +9700,7 @@
       <c r="I58" t="n">
         <v>12.55</v>
       </c>
-      <c r="J58" s="1" t="n">
+      <c r="J58" s="2" t="n">
         <v>45048</v>
       </c>
       <c r="K58" t="n">
@@ -9701,13 +9713,13 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45017</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="C59" s="1" t="n">
+      <c r="C59" s="2" t="n">
         <v>45140</v>
       </c>
       <c r="D59" t="inlineStr">
@@ -9734,7 +9746,7 @@
       <c r="I59" t="n">
         <v>12.94</v>
       </c>
-      <c r="J59" s="1" t="n">
+      <c r="J59" s="2" t="n">
         <v>45140</v>
       </c>
       <c r="K59" t="n">
@@ -9747,13 +9759,13 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45108</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="C60" s="1" t="n">
+      <c r="C60" s="2" t="n">
         <v>45237</v>
       </c>
       <c r="D60" t="inlineStr">
@@ -9780,7 +9792,7 @@
       <c r="I60" t="n">
         <v>13.32</v>
       </c>
-      <c r="J60" s="1" t="n">
+      <c r="J60" s="2" t="n">
         <v>45237</v>
       </c>
       <c r="K60" t="n">
@@ -9793,13 +9805,13 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45200</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45291</v>
       </c>
-      <c r="C61" s="1" t="n">
+      <c r="C61" s="2" t="n">
         <v>45337</v>
       </c>
       <c r="D61" t="inlineStr">
@@ -9826,7 +9838,7 @@
       <c r="I61" t="n">
         <v>13.89</v>
       </c>
-      <c r="J61" s="1" t="n">
+      <c r="J61" s="2" t="n">
         <v>45337</v>
       </c>
       <c r="K61" t="n">
@@ -9839,13 +9851,13 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45292</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="C62" s="1" t="n">
+      <c r="C62" s="2" t="n">
         <v>45419</v>
       </c>
       <c r="D62" t="inlineStr">
@@ -9872,7 +9884,7 @@
       <c r="I62" t="n">
         <v>15.41</v>
       </c>
-      <c r="J62" s="1" t="n">
+      <c r="J62" s="2" t="n">
         <v>45419</v>
       </c>
       <c r="K62" t="n">
@@ -9885,13 +9897,13 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45383</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="C63" s="1" t="n">
+      <c r="C63" s="2" t="n">
         <v>45506</v>
       </c>
       <c r="D63" t="inlineStr">
@@ -9918,7 +9930,7 @@
       <c r="I63" t="n">
         <v>-2.029999999999999</v>
       </c>
-      <c r="J63" s="1" t="n">
+      <c r="J63" s="2" t="n">
         <v>45506</v>
       </c>
       <c r="K63" t="n">
@@ -9931,13 +9943,13 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45474</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45565</v>
       </c>
-      <c r="C64" s="1" t="n">
+      <c r="C64" s="2" t="n">
         <v>45601</v>
       </c>
       <c r="D64" t="inlineStr">
@@ -9964,7 +9976,7 @@
       <c r="I64" t="n">
         <v>-1.989999999999998</v>
       </c>
-      <c r="J64" s="1" t="n">
+      <c r="J64" s="2" t="n">
         <v>45601</v>
       </c>
       <c r="K64" t="n">
@@ -9977,13 +9989,13 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45566</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45657</v>
       </c>
-      <c r="C65" s="1" t="n">
+      <c r="C65" s="2" t="n">
         <v>45701</v>
       </c>
       <c r="D65" t="inlineStr">
@@ -10010,7 +10022,7 @@
       <c r="I65" t="n">
         <v>-2.079999999999998</v>
       </c>
-      <c r="J65" s="1" t="n">
+      <c r="J65" s="2" t="n">
         <v>45701</v>
       </c>
       <c r="K65" t="n">
@@ -10023,13 +10035,13 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45658</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="C66" s="1" t="n">
+      <c r="C66" s="2" t="n">
         <v>45783</v>
       </c>
       <c r="D66" t="inlineStr">
@@ -10056,7 +10068,7 @@
       <c r="I66" t="n">
         <v>-3.799999999999999</v>
       </c>
-      <c r="J66" s="1" t="n">
+      <c r="J66" s="2" t="n">
         <v>45783</v>
       </c>
       <c r="K66" t="n">
@@ -10069,13 +10081,13 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45748</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="C67" s="1" t="n">
+      <c r="C67" s="2" t="n">
         <v>45874</v>
       </c>
       <c r="D67" t="inlineStr">
@@ -10102,7 +10114,7 @@
       <c r="I67" t="n">
         <v>14.11</v>
       </c>
-      <c r="J67" s="1" t="n">
+      <c r="J67" s="2" t="n">
         <v>45874</v>
       </c>
       <c r="K67" t="n">
@@ -10115,13 +10127,13 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>45839</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>45930</v>
       </c>
-      <c r="C68" s="1" t="n">
+      <c r="C68" s="2" t="n">
         <v>45965</v>
       </c>
       <c r="D68" t="inlineStr">
@@ -10148,7 +10160,7 @@
       <c r="I68" t="n">
         <v>14.3</v>
       </c>
-      <c r="J68" s="1" t="n">
+      <c r="J68" s="2" t="n">
         <v>45965</v>
       </c>
       <c r="K68" t="n">
@@ -10161,13 +10173,13 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>45931</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>46022</v>
       </c>
-      <c r="C69" s="1" t="n">
+      <c r="C69" s="2" t="n">
         <v>46066</v>
       </c>
       <c r="D69" t="inlineStr">
@@ -10194,7 +10206,7 @@
       <c r="I69" t="n">
         <v>15.32</v>
       </c>
-      <c r="J69" s="1" t="n">
+      <c r="J69" s="2" t="n">
         <v>46066</v>
       </c>
       <c r="K69" t="n">
@@ -10207,13 +10219,13 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>46023</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>46112</v>
       </c>
-      <c r="C70" s="1" t="n">
+      <c r="C70" s="2" t="n">
         <v>46147</v>
       </c>
       <c r="D70" t="inlineStr">
@@ -10240,7 +10252,7 @@
       <c r="I70" t="n">
         <v>16.85</v>
       </c>
-      <c r="J70" s="1" t="n">
+      <c r="J70" s="2" t="n">
         <v>46147</v>
       </c>
       <c r="K70" t="n">
@@ -10253,13 +10265,13 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>46113</v>
       </c>
-      <c r="B71" s="1" t="n">
+      <c r="B71" s="2" t="n">
         <v>46203</v>
       </c>
-      <c r="C71" s="1" t="n">
+      <c r="C71" s="2" t="n">
         <v>46238</v>
       </c>
       <c r="D71" t="inlineStr">
@@ -10286,7 +10298,7 @@
       <c r="I71" t="n">
         <v>17.17</v>
       </c>
-      <c r="J71" s="1" t="n">
+      <c r="J71" s="2" t="n">
         <v>46238</v>
       </c>
       <c r="K71" t="n">
@@ -10323,52 +10335,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>acciones</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>40290</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>40301</v>
       </c>
       <c r="C2" t="n">
@@ -10397,10 +10409,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>40388</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>40393</v>
       </c>
       <c r="C3" t="n">
@@ -10429,10 +10441,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>40472</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>40479</v>
       </c>
       <c r="C4" t="n">
@@ -10461,10 +10473,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>40583</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40591</v>
       </c>
       <c r="C5" t="n">
@@ -10493,10 +10505,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40661</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40669</v>
       </c>
       <c r="C6" t="n">
@@ -10525,10 +10537,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40753</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40764</v>
       </c>
       <c r="C7" t="n">
@@ -10557,10 +10569,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40844</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40850</v>
       </c>
       <c r="C8" t="n">
@@ -10589,10 +10601,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40947</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40961</v>
       </c>
       <c r="C9" t="n">
@@ -10621,10 +10633,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>41026</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>41039</v>
       </c>
       <c r="C10" t="n">
@@ -10653,10 +10665,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>41117</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>41129</v>
       </c>
       <c r="C11" t="n">
@@ -10685,10 +10697,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>41208</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>41219</v>
       </c>
       <c r="C12" t="n">
@@ -10717,10 +10729,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>41320</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>41334</v>
       </c>
       <c r="C13" t="n">
@@ -10749,10 +10761,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>41390</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>41402</v>
       </c>
       <c r="C14" t="n">
@@ -10781,10 +10793,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>41481</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>41488</v>
       </c>
       <c r="C15" t="n">
@@ -10813,10 +10825,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41578</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41585</v>
       </c>
       <c r="C16" t="n">
@@ -10845,10 +10857,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41675</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41681</v>
       </c>
       <c r="C17" t="n">
@@ -10877,10 +10889,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41754</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41764</v>
       </c>
       <c r="C18" t="n">
@@ -10909,10 +10921,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41845</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="C19" t="n">
@@ -10941,10 +10953,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41943</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41949</v>
       </c>
       <c r="C20" t="n">
@@ -10973,10 +10985,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>42035</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>42048</v>
       </c>
       <c r="C21" t="n">
@@ -11005,10 +11017,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>42118</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>42128</v>
       </c>
       <c r="C22" t="n">
@@ -11037,10 +11049,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>42209</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>42220</v>
       </c>
       <c r="C23" t="n">
@@ -11069,10 +11081,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>42300</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>42307</v>
       </c>
       <c r="C24" t="n">
@@ -11101,10 +11113,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>42400</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>42416</v>
       </c>
       <c r="C25" t="n">
@@ -11133,10 +11145,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>42480</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42493</v>
       </c>
       <c r="C26" t="n">
@@ -11165,10 +11177,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42573</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42583</v>
       </c>
       <c r="C27" t="n">
@@ -11197,10 +11209,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42664</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="C28" t="n">
@@ -11229,10 +11241,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42776</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42789</v>
       </c>
       <c r="C29" t="n">
@@ -11261,10 +11273,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42846</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42853</v>
       </c>
       <c r="C30" t="n">
@@ -11293,10 +11305,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42937</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42944</v>
       </c>
       <c r="C31" t="n">
@@ -11325,10 +11337,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>43028</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>43038</v>
       </c>
       <c r="C32" t="n">
@@ -11357,10 +11369,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>43131</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>43146</v>
       </c>
       <c r="C33" t="n">
@@ -11389,10 +11401,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>43210</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>43217</v>
       </c>
       <c r="C34" t="n">
@@ -11421,10 +11433,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>43301</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>43307</v>
       </c>
       <c r="C35" t="n">
@@ -11453,10 +11465,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>43392</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>43398</v>
       </c>
       <c r="C36" t="n">
@@ -11485,10 +11497,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>43496</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43509</v>
       </c>
       <c r="C37" t="n">
@@ -11517,10 +11529,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43579</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43586</v>
       </c>
       <c r="C38" t="n">
@@ -11549,10 +11561,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43672</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43678</v>
       </c>
       <c r="C39" t="n">
@@ -11581,10 +11593,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43756</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="C40" t="n">
@@ -11613,10 +11625,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43861</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43874</v>
       </c>
       <c r="C41" t="n">
@@ -11645,10 +11657,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43945</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43952</v>
       </c>
       <c r="C42" t="n">
@@ -11677,10 +11689,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>44035</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="C43" t="n">
@@ -11709,10 +11721,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>44127</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>44134</v>
       </c>
       <c r="C44" t="n">
@@ -11741,10 +11753,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>44227</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>44238</v>
       </c>
       <c r="C45" t="n">
@@ -11773,10 +11785,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>44308</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="C46" t="n">
@@ -11805,10 +11817,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>44400</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>44407</v>
       </c>
       <c r="C47" t="n">
@@ -11837,10 +11849,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44498</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44503</v>
       </c>
       <c r="C48" t="n">
@@ -11869,10 +11881,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44592</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44601</v>
       </c>
       <c r="C49" t="n">
@@ -11901,10 +11913,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44680</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44687</v>
       </c>
       <c r="C50" t="n">
@@ -11933,10 +11945,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44771</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44778</v>
       </c>
       <c r="C51" t="n">
@@ -11965,10 +11977,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44855</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44862</v>
       </c>
       <c r="C52" t="n">
@@ -11997,10 +12009,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44957</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44967</v>
       </c>
       <c r="C53" t="n">
@@ -12029,10 +12041,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>45041</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>45048</v>
       </c>
       <c r="C54" t="n">
@@ -12061,10 +12073,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>45138</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>45140</v>
       </c>
       <c r="C55" t="n">
@@ -12093,10 +12105,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>45230</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>45237</v>
       </c>
       <c r="C56" t="n">
@@ -12125,10 +12137,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>45331</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>45337</v>
       </c>
       <c r="C57" t="n">
@@ -12157,10 +12169,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45412</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>45419</v>
       </c>
       <c r="C58" t="n">
@@ -12189,10 +12201,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45504</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45506</v>
       </c>
       <c r="C59" t="n">
@@ -12221,10 +12233,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45596</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45601</v>
       </c>
       <c r="C60" t="n">
@@ -12253,10 +12265,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45695</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45701</v>
       </c>
       <c r="C61" t="n">
@@ -12285,10 +12297,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45777</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45783</v>
       </c>
       <c r="C62" t="n">
@@ -12317,10 +12329,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45869</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45874</v>
       </c>
       <c r="C63" t="n">
@@ -12349,10 +12361,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45961</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45965</v>
       </c>
       <c r="C64" t="n">
@@ -12381,10 +12393,10 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>46059</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>46066</v>
       </c>
       <c r="C65" t="n">
@@ -12413,10 +12425,10 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>46142</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>46147</v>
       </c>
       <c r="C66" t="n">
@@ -12445,10 +12457,10 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>46234</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>46238</v>
       </c>
       <c r="C67" t="n">
@@ -12495,12 +12507,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>campo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>
